--- a/7_map_metadata/Metadata_Mappings_Initial.xlsx
+++ b/7_map_metadata/Metadata_Mappings_Initial.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/srp33/GitRepos/Prepare_AnnotatedBCGEData/7_map_metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A19B58-210A-D843-9AE4-4E7D762BEA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E084D61D-12B9-4C47-8534-E4C90C2CB58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="51200" windowHeight="26320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categorical" sheetId="2" r:id="rId1"/>
     <sheet name="Numeric" sheetId="3" r:id="rId2"/>
-    <sheet name="TODO" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16759" uniqueCount="2773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16754" uniqueCount="2768">
   <si>
     <t>dataset</t>
   </si>
@@ -8183,21 +8182,9 @@
     <t>unknown||unkown</t>
   </si>
   <si>
-    <t>Use code and manual review to check for consistency and errors.</t>
-  </si>
-  <si>
-    <t>Generate a new spreadsheet in which orig_values are split out?</t>
-  </si>
-  <si>
-    <t>Populate all of the orig_values that are empty (first empty the ones that are incomplete)?</t>
-  </si>
-  <si>
     <t>Grade 1 (Code C28077)||Or (Code C37998)||Grade 2 (Code C28078)</t>
   </si>
   <si>
-    <t>Check for duplicates. I know there's at least one: GSE61304	t_extent_of_primary_tumor	Disease Stage Qualifier (Code C28108)	Not Applicable (Code C48660)	NA</t>
-  </si>
-  <si>
     <t>Present (Code C25626)</t>
   </si>
   <si>
@@ -8205,9 +8192,6 @@
   </si>
   <si>
     <t>This overlaps with the &lt;25 value.</t>
-  </si>
-  <si>
-    <t>Use script to add primitive data type to every entry, based on which tab it's in.</t>
   </si>
   <si>
     <t>Percentage (Code C25613)||Range (Code C38013)</t>
@@ -8557,7 +8541,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8576,13 +8560,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -8667,7 +8644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8684,8 +8661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -9588,9 +9564,9 @@
         <v>1927</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2672</v>
-      </c>
-      <c r="E22" s="8" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>1968</v>
       </c>
       <c r="F22" s="3"/>
@@ -9606,9 +9582,9 @@
         <v>1927</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2672</v>
-      </c>
-      <c r="E23" s="8" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>1967</v>
       </c>
       <c r="F23" s="3"/>
@@ -9626,7 +9602,7 @@
       <c r="D24" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>1337</v>
       </c>
       <c r="F24" s="3"/>
@@ -9642,9 +9618,9 @@
         <v>1927</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2666</v>
-      </c>
-      <c r="E25" s="13" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>2644</v>
       </c>
       <c r="F25" s="3"/>
@@ -9662,7 +9638,7 @@
       <c r="D26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>2544</v>
       </c>
       <c r="F26" s="3"/>
@@ -9678,13 +9654,13 @@
         <v>1927</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2666</v>
-      </c>
-      <c r="E27" s="13" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>2544</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2706</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -9698,7 +9674,7 @@
         <v>1927</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>1967</v>
@@ -9716,7 +9692,7 @@
         <v>1927</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>1968</v>
@@ -9734,7 +9710,7 @@
         <v>1919</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
@@ -9754,7 +9730,7 @@
         <v>1919</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E31" s="3">
         <v>1</v>
@@ -9774,7 +9750,7 @@
         <v>1919</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>1337</v>
@@ -9792,7 +9768,7 @@
         <v>1919</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>706</v>
@@ -9810,7 +9786,7 @@
         <v>1919</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
@@ -9829,8 +9805,8 @@
       <c r="C35" s="3" t="s">
         <v>1919</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>2666</v>
+      <c r="D35" s="8" t="s">
+        <v>2661</v>
       </c>
       <c r="E35" s="3">
         <v>1</v>
@@ -14442,7 +14418,7 @@
       <c r="D290" s="3" t="s">
         <v>2476</v>
       </c>
-      <c r="E290" s="13">
+      <c r="E290" s="12">
         <v>0</v>
       </c>
       <c r="F290" s="3"/>
@@ -14460,7 +14436,7 @@
       <c r="D291" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E291" s="13">
+      <c r="E291" s="12">
         <v>1</v>
       </c>
       <c r="F291" s="3"/>
@@ -14479,7 +14455,7 @@
         <v>60</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>2696</v>
+        <v>2691</v>
       </c>
       <c r="F292" s="3"/>
     </row>
@@ -14497,7 +14473,7 @@
         <v>60</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>2697</v>
+        <v>2692</v>
       </c>
       <c r="F293" s="3"/>
     </row>
@@ -14515,7 +14491,7 @@
         <v>60</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="F294" s="3"/>
     </row>
@@ -14533,7 +14509,7 @@
         <v>60</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>2699</v>
+        <v>2694</v>
       </c>
       <c r="F295" s="3"/>
     </row>
@@ -14658,7 +14634,7 @@
       <c r="D302" s="3" t="s">
         <v>2107</v>
       </c>
-      <c r="E302" s="13" t="s">
+      <c r="E302" s="12" t="s">
         <v>2567</v>
       </c>
       <c r="F302" s="3"/>
@@ -14676,7 +14652,7 @@
       <c r="D303" s="3" t="s">
         <v>2108</v>
       </c>
-      <c r="E303" s="13" t="s">
+      <c r="E303" s="12" t="s">
         <v>2568</v>
       </c>
       <c r="F303" s="3"/>
@@ -14694,7 +14670,7 @@
       <c r="D304" s="3" t="s">
         <v>2570</v>
       </c>
-      <c r="E304" s="13" t="s">
+      <c r="E304" s="12" t="s">
         <v>2569</v>
       </c>
       <c r="F304" s="3"/>
@@ -18055,12 +18031,12 @@
         <v>2538</v>
       </c>
       <c r="C488" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1349</v>
       </c>
-      <c r="E488" s="13" t="s">
+      <c r="E488" s="12" t="s">
         <v>2571</v>
       </c>
       <c r="F488" s="3"/>
@@ -18073,12 +18049,12 @@
         <v>2538</v>
       </c>
       <c r="C489" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E489" s="13" t="s">
+      <c r="E489" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F489" s="3"/>
@@ -20376,7 +20352,7 @@
       <c r="D613" s="3" t="s">
         <v>2523</v>
       </c>
-      <c r="E613" s="13">
+      <c r="E613" s="12">
         <v>0</v>
       </c>
       <c r="F613" s="3"/>
@@ -20394,7 +20370,7 @@
       <c r="D614" s="3" t="s">
         <v>2457</v>
       </c>
-      <c r="E614" s="13">
+      <c r="E614" s="12">
         <v>1</v>
       </c>
       <c r="F614" s="3"/>
@@ -20412,7 +20388,7 @@
       <c r="D615" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E615" s="13" t="s">
+      <c r="E615" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F615" s="3"/>
@@ -22056,7 +22032,7 @@
       <c r="D703" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="E703" s="13" t="s">
+      <c r="E703" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F703" s="3"/>
@@ -22074,7 +22050,7 @@
       <c r="D704" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="E704" s="13" t="s">
+      <c r="E704" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F704" s="3"/>
@@ -22092,7 +22068,7 @@
       <c r="D705" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E705" s="13" t="s">
+      <c r="E705" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F705" s="3"/>
@@ -23118,7 +23094,7 @@
       <c r="D762" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="E762" s="13" t="s">
+      <c r="E762" s="12" t="s">
         <v>956</v>
       </c>
     </row>
@@ -23135,7 +23111,7 @@
       <c r="D763" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="E763" s="13" t="s">
+      <c r="E763" s="12" t="s">
         <v>950</v>
       </c>
     </row>
@@ -23152,7 +23128,7 @@
       <c r="D764" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="E764" s="13" t="s">
+      <c r="E764" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F764" s="3"/>
@@ -23170,7 +23146,7 @@
       <c r="D765" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="E765" s="13" t="s">
+      <c r="E765" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F765" s="3"/>
@@ -23188,7 +23164,7 @@
       <c r="D766" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E766" s="13" t="s">
+      <c r="E766" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F766" s="3"/>
@@ -23206,7 +23182,7 @@
       <c r="D767" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="E767" s="13" t="s">
+      <c r="E767" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F767" s="3"/>
@@ -23224,7 +23200,7 @@
       <c r="D768" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="E768" s="13" t="s">
+      <c r="E768" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F768" s="3"/>
@@ -24258,9 +24234,9 @@
         <v>1411</v>
       </c>
       <c r="D825" s="3" t="s">
-        <v>2659</v>
-      </c>
-      <c r="E825" s="13" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E825" s="12" t="s">
         <v>2559</v>
       </c>
       <c r="F825" s="3"/>
@@ -24276,9 +24252,9 @@
         <v>1411</v>
       </c>
       <c r="D826" s="3" t="s">
-        <v>2659</v>
-      </c>
-      <c r="E826" s="13" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E826" s="12" t="s">
         <v>2559</v>
       </c>
     </row>
@@ -24347,13 +24323,13 @@
         <v>1411</v>
       </c>
       <c r="D830" s="3" t="s">
-        <v>2662</v>
+        <v>2657</v>
       </c>
       <c r="E830" s="3" t="s">
         <v>1966</v>
       </c>
       <c r="F830" s="3" t="s">
-        <v>2663</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="831" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -24373,7 +24349,7 @@
         <v>1966</v>
       </c>
       <c r="F831" s="3" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="832" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -24387,13 +24363,13 @@
         <v>1411</v>
       </c>
       <c r="D832" s="3" t="s">
-        <v>2664</v>
+        <v>2659</v>
       </c>
       <c r="E832" s="3" t="s">
         <v>1518</v>
       </c>
       <c r="F832" s="3" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="833" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -24413,7 +24389,7 @@
         <v>1518</v>
       </c>
       <c r="F833" s="3" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="834" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -24433,7 +24409,7 @@
         <v>1519</v>
       </c>
       <c r="F834" s="3" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="835" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -27873,7 +27849,7 @@
         <v>1465</v>
       </c>
       <c r="D1024" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1024" s="3" t="s">
         <v>1473</v>
@@ -27963,7 +27939,7 @@
         <v>1465</v>
       </c>
       <c r="D1029" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1029" s="3" t="s">
         <v>1473</v>
@@ -28071,7 +28047,7 @@
         <v>1465</v>
       </c>
       <c r="D1035" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1035" s="3" t="s">
         <v>1473</v>
@@ -28161,7 +28137,7 @@
         <v>1465</v>
       </c>
       <c r="D1040" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1040" s="3" t="s">
         <v>1473</v>
@@ -28287,7 +28263,7 @@
         <v>1465</v>
       </c>
       <c r="D1047" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1047" s="3" t="s">
         <v>1473</v>
@@ -28377,7 +28353,7 @@
         <v>1465</v>
       </c>
       <c r="D1052" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1052" s="3" t="s">
         <v>1473</v>
@@ -28467,7 +28443,7 @@
         <v>1465</v>
       </c>
       <c r="D1057" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1057" s="3" t="s">
         <v>1473</v>
@@ -28647,7 +28623,7 @@
         <v>1465</v>
       </c>
       <c r="D1067" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1067" s="3" t="s">
         <v>1473</v>
@@ -28737,7 +28713,7 @@
         <v>1465</v>
       </c>
       <c r="D1072" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1072" s="3" t="s">
         <v>1473</v>
@@ -28827,7 +28803,7 @@
         <v>1465</v>
       </c>
       <c r="D1077" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1077" s="3" t="s">
         <v>1473</v>
@@ -28917,7 +28893,7 @@
         <v>1465</v>
       </c>
       <c r="D1082" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1082" s="3" t="s">
         <v>1473</v>
@@ -29189,7 +29165,7 @@
         <v>1465</v>
       </c>
       <c r="D1097" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1097" s="3" t="s">
         <v>1473</v>
@@ -29369,7 +29345,7 @@
         <v>1465</v>
       </c>
       <c r="D1107" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1107" s="3" t="s">
         <v>1473</v>
@@ -29459,7 +29435,7 @@
         <v>1465</v>
       </c>
       <c r="D1112" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1112" s="3" t="s">
         <v>1473</v>
@@ -29549,7 +29525,7 @@
         <v>1465</v>
       </c>
       <c r="D1117" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1117" s="3" t="s">
         <v>1473</v>
@@ -29675,7 +29651,7 @@
         <v>1465</v>
       </c>
       <c r="D1124" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1124" s="3" t="s">
         <v>1473</v>
@@ -29765,7 +29741,7 @@
         <v>1465</v>
       </c>
       <c r="D1129" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1129" s="3" t="s">
         <v>1473</v>
@@ -29942,10 +29918,10 @@
         <v>309</v>
       </c>
       <c r="C1139" s="3" t="s">
-        <v>2667</v>
-      </c>
-      <c r="D1139" s="9" t="s">
-        <v>2666</v>
+        <v>2662</v>
+      </c>
+      <c r="D1139" s="8" t="s">
+        <v>2661</v>
       </c>
       <c r="E1139" s="3" t="s">
         <v>959</v>
@@ -29962,10 +29938,10 @@
         <v>309</v>
       </c>
       <c r="C1140" s="3" t="s">
-        <v>2667</v>
-      </c>
-      <c r="D1140" s="9" t="s">
-        <v>2666</v>
+        <v>2662</v>
+      </c>
+      <c r="D1140" s="8" t="s">
+        <v>2661</v>
       </c>
       <c r="E1140" s="3" t="s">
         <v>960</v>
@@ -29982,7 +29958,7 @@
         <v>309</v>
       </c>
       <c r="C1141" s="3" t="s">
-        <v>2667</v>
+        <v>2662</v>
       </c>
       <c r="D1141" s="3" t="s">
         <v>1336</v>
@@ -30241,7 +30217,7 @@
       <c r="D1155" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="E1155" s="13" t="s">
+      <c r="E1155" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F1155" s="3"/>
@@ -30259,7 +30235,7 @@
       <c r="D1156" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="E1156" s="13" t="s">
+      <c r="E1156" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F1156" s="3"/>
@@ -30277,7 +30253,7 @@
       <c r="D1157" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1157" s="13" t="s">
+      <c r="E1157" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1157" s="3"/>
@@ -30817,7 +30793,7 @@
       <c r="D1187" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="E1187" s="13" t="s">
+      <c r="E1187" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F1187" s="3"/>
@@ -30835,7 +30811,7 @@
       <c r="D1188" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="E1188" s="13" t="s">
+      <c r="E1188" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F1188" s="3"/>
@@ -30853,7 +30829,7 @@
       <c r="D1189" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1189" s="13" t="s">
+      <c r="E1189" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1189" s="3"/>
@@ -30871,7 +30847,7 @@
       <c r="D1190" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="E1190" s="13" t="s">
+      <c r="E1190" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F1190" s="3"/>
@@ -30889,7 +30865,7 @@
       <c r="D1191" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="E1191" s="13" t="s">
+      <c r="E1191" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F1191" s="3"/>
@@ -30907,7 +30883,7 @@
       <c r="D1192" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1192" s="13" t="s">
+      <c r="E1192" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1192" s="3"/>
@@ -30979,7 +30955,7 @@
       <c r="D1196" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="E1196" s="13" t="s">
+      <c r="E1196" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F1196" s="3"/>
@@ -30997,7 +30973,7 @@
       <c r="D1197" s="3" t="s">
         <v>1434</v>
       </c>
-      <c r="E1197" s="13" t="s">
+      <c r="E1197" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F1197" s="3"/>
@@ -33803,7 +33779,7 @@
         <v>1465</v>
       </c>
       <c r="D1353" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1353" s="3" t="s">
         <v>1473</v>
@@ -33893,7 +33869,7 @@
         <v>1465</v>
       </c>
       <c r="D1358" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E1358" s="3" t="s">
         <v>1473</v>
@@ -37103,7 +37079,7 @@
       <c r="D1535" s="3" t="s">
         <v>1375</v>
       </c>
-      <c r="E1535" s="13" t="s">
+      <c r="E1535" s="12" t="s">
         <v>1642</v>
       </c>
       <c r="F1535" s="3"/>
@@ -37121,7 +37097,7 @@
       <c r="D1536" s="3" t="s">
         <v>1548</v>
       </c>
-      <c r="E1536" s="13" t="s">
+      <c r="E1536" s="12" t="s">
         <v>1531</v>
       </c>
       <c r="F1536" s="3"/>
@@ -37139,7 +37115,7 @@
       <c r="D1537" s="3" t="s">
         <v>2577</v>
       </c>
-      <c r="E1537" s="13" t="s">
+      <c r="E1537" s="12" t="s">
         <v>884</v>
       </c>
       <c r="F1537" s="3"/>
@@ -37157,7 +37133,7 @@
       <c r="D1538" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="E1538" s="13" t="s">
+      <c r="E1538" s="12" t="s">
         <v>2573</v>
       </c>
       <c r="F1538" s="3"/>
@@ -37175,7 +37151,7 @@
       <c r="D1539" s="3" t="s">
         <v>2578</v>
       </c>
-      <c r="E1539" s="13" t="s">
+      <c r="E1539" s="12" t="s">
         <v>2574</v>
       </c>
       <c r="F1539" s="3"/>
@@ -37190,10 +37166,10 @@
       <c r="C1540" s="3" t="s">
         <v>1321</v>
       </c>
-      <c r="D1540" s="15" t="s">
+      <c r="D1540" s="14" t="s">
         <v>1336</v>
       </c>
-      <c r="E1540" s="13" t="s">
+      <c r="E1540" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1540" s="3"/>
@@ -37321,13 +37297,13 @@
         <v>1667</v>
       </c>
       <c r="D1547" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1547" s="3" t="s">
         <v>1961</v>
       </c>
       <c r="F1547" s="3" t="s">
-        <v>2660</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="1548" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -37341,13 +37317,13 @@
         <v>1667</v>
       </c>
       <c r="D1548" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1548" s="3" t="s">
         <v>1962</v>
       </c>
       <c r="F1548" s="3" t="s">
-        <v>2660</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="1549" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -37360,10 +37336,10 @@
       <c r="C1549" s="3" t="s">
         <v>1667</v>
       </c>
-      <c r="D1549" s="15" t="s">
+      <c r="D1549" s="14" t="s">
         <v>1668</v>
       </c>
-      <c r="E1549" s="13" t="s">
+      <c r="E1549" s="12" t="s">
         <v>881</v>
       </c>
       <c r="F1549" s="3" t="s">
@@ -37380,10 +37356,10 @@
       <c r="C1550" s="3" t="s">
         <v>1667</v>
       </c>
-      <c r="D1550" s="16" t="s">
+      <c r="D1550" s="15" t="s">
         <v>1669</v>
       </c>
-      <c r="E1550" s="13" t="s">
+      <c r="E1550" s="12" t="s">
         <v>880</v>
       </c>
       <c r="F1550" s="3" t="s">
@@ -37400,10 +37376,10 @@
       <c r="C1551" s="3" t="s">
         <v>1667</v>
       </c>
-      <c r="D1551" s="15" t="s">
+      <c r="D1551" s="14" t="s">
         <v>1336</v>
       </c>
-      <c r="E1551" s="13" t="s">
+      <c r="E1551" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1551" s="3" t="s">
@@ -37420,10 +37396,10 @@
       <c r="C1552" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D1552" s="15" t="s">
+      <c r="D1552" s="14" t="s">
         <v>1668</v>
       </c>
-      <c r="E1552" s="13" t="s">
+      <c r="E1552" s="12" t="s">
         <v>881</v>
       </c>
       <c r="F1552" s="3" t="s">
@@ -37440,10 +37416,10 @@
       <c r="C1553" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D1553" s="16" t="s">
+      <c r="D1553" s="15" t="s">
         <v>1669</v>
       </c>
-      <c r="E1553" s="13" t="s">
+      <c r="E1553" s="12" t="s">
         <v>880</v>
       </c>
       <c r="F1553" s="3" t="s">
@@ -37697,7 +37673,7 @@
       <c r="D1567" s="3" t="s">
         <v>2071</v>
       </c>
-      <c r="E1567" s="13" t="s">
+      <c r="E1567" s="12" t="s">
         <v>2579</v>
       </c>
       <c r="F1567" s="3"/>
@@ -37715,7 +37691,7 @@
       <c r="D1568" s="3" t="s">
         <v>2080</v>
       </c>
-      <c r="E1568" s="13" t="s">
+      <c r="E1568" s="12" t="s">
         <v>2580</v>
       </c>
       <c r="F1568" s="3"/>
@@ -37730,10 +37706,10 @@
       <c r="C1569" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D1569" s="15" t="s">
+      <c r="D1569" s="14" t="s">
         <v>1336</v>
       </c>
-      <c r="E1569" s="13" t="s">
+      <c r="E1569" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1569" s="3"/>
@@ -37805,7 +37781,7 @@
       <c r="D1573" s="3" t="s">
         <v>2071</v>
       </c>
-      <c r="E1573" s="13" t="s">
+      <c r="E1573" s="12" t="s">
         <v>2579</v>
       </c>
       <c r="F1573" s="3"/>
@@ -37823,7 +37799,7 @@
       <c r="D1574" s="3" t="s">
         <v>2080</v>
       </c>
-      <c r="E1574" s="13" t="s">
+      <c r="E1574" s="12" t="s">
         <v>2580</v>
       </c>
       <c r="F1574" s="3"/>
@@ -37838,10 +37814,10 @@
       <c r="C1575" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D1575" s="15" t="s">
+      <c r="D1575" s="14" t="s">
         <v>1336</v>
       </c>
-      <c r="E1575" s="13" t="s">
+      <c r="E1575" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1575" s="3"/>
@@ -37911,7 +37887,7 @@
         <v>382</v>
       </c>
       <c r="D1579" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1579" s="3" t="s">
         <v>984</v>
@@ -37929,7 +37905,7 @@
         <v>382</v>
       </c>
       <c r="D1580" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1580" s="3" t="s">
         <v>1337</v>
@@ -38009,7 +37985,7 @@
       <c r="D1584" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="E1584" s="13">
+      <c r="E1584" s="12">
         <v>0</v>
       </c>
       <c r="F1584" s="3"/>
@@ -38027,7 +38003,7 @@
       <c r="D1585" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="E1585" s="13">
+      <c r="E1585" s="12">
         <v>1</v>
       </c>
       <c r="F1585" s="3"/>
@@ -38045,7 +38021,7 @@
       <c r="D1586" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1586" s="13" t="s">
+      <c r="E1586" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1586" s="3"/>
@@ -38063,7 +38039,7 @@
       <c r="D1587" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="E1587" s="13">
+      <c r="E1587" s="12">
         <v>0</v>
       </c>
       <c r="F1587" s="3"/>
@@ -38081,7 +38057,7 @@
       <c r="D1588" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="E1588" s="13">
+      <c r="E1588" s="12">
         <v>1</v>
       </c>
       <c r="F1588" s="3"/>
@@ -38099,7 +38075,7 @@
       <c r="D1589" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1589" s="13" t="s">
+      <c r="E1589" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1589" s="3"/>
@@ -38117,7 +38093,7 @@
       <c r="D1590" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="E1590" s="13" t="s">
+      <c r="E1590" s="12" t="s">
         <v>711</v>
       </c>
       <c r="F1590" s="3"/>
@@ -38135,7 +38111,7 @@
       <c r="D1591" s="3" t="s">
         <v>1679</v>
       </c>
-      <c r="E1591" s="13" t="s">
+      <c r="E1591" s="12" t="s">
         <v>1680</v>
       </c>
       <c r="F1591" s="3"/>
@@ -38153,7 +38129,7 @@
       <c r="D1592" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="E1592" s="13" t="s">
+      <c r="E1592" s="12" t="s">
         <v>1682</v>
       </c>
       <c r="F1592" s="3"/>
@@ -38171,7 +38147,7 @@
       <c r="D1593" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1593" s="13" t="s">
+      <c r="E1593" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1593" s="3"/>
@@ -38189,7 +38165,7 @@
       <c r="D1594" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="E1594" s="13" t="s">
+      <c r="E1594" s="12" t="s">
         <v>711</v>
       </c>
       <c r="F1594" s="3"/>
@@ -38207,7 +38183,7 @@
       <c r="D1595" s="3" t="s">
         <v>1679</v>
       </c>
-      <c r="E1595" s="13" t="s">
+      <c r="E1595" s="12" t="s">
         <v>1680</v>
       </c>
       <c r="F1595" s="3"/>
@@ -38225,7 +38201,7 @@
       <c r="D1596" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="E1596" s="13" t="s">
+      <c r="E1596" s="12" t="s">
         <v>1682</v>
       </c>
       <c r="F1596" s="3"/>
@@ -38243,7 +38219,7 @@
       <c r="D1597" s="3" t="s">
         <v>1672</v>
       </c>
-      <c r="E1597" s="13" t="s">
+      <c r="E1597" s="12" t="s">
         <v>711</v>
       </c>
       <c r="F1597" s="3"/>
@@ -38261,7 +38237,7 @@
       <c r="D1598" s="3" t="s">
         <v>1679</v>
       </c>
-      <c r="E1598" s="13" t="s">
+      <c r="E1598" s="12" t="s">
         <v>1680</v>
       </c>
       <c r="F1598" s="3"/>
@@ -38279,7 +38255,7 @@
       <c r="D1599" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="E1599" s="13" t="s">
+      <c r="E1599" s="12" t="s">
         <v>1682</v>
       </c>
       <c r="F1599" s="3"/>
@@ -38297,7 +38273,7 @@
       <c r="D1600" s="3" t="s">
         <v>1684</v>
       </c>
-      <c r="E1600" s="13" t="s">
+      <c r="E1600" s="12" t="s">
         <v>1685</v>
       </c>
       <c r="F1600" s="3"/>
@@ -38315,7 +38291,7 @@
       <c r="D1601" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1601" s="13" t="s">
+      <c r="E1601" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1601" s="3"/>
@@ -41015,7 +40991,7 @@
         <v>2267</v>
       </c>
       <c r="D1749" s="3" t="s">
-        <v>2656</v>
+        <v>2652</v>
       </c>
       <c r="E1749" s="3" t="s">
         <v>891</v>
@@ -41033,7 +41009,7 @@
         <v>2267</v>
       </c>
       <c r="D1750" s="3" t="s">
-        <v>2655</v>
+        <v>2651</v>
       </c>
       <c r="E1750" s="3" t="s">
         <v>892</v>
@@ -42521,7 +42497,7 @@
       <c r="D1832" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="E1832" s="13">
+      <c r="E1832" s="12">
         <v>1</v>
       </c>
       <c r="F1832" s="3"/>
@@ -42539,7 +42515,7 @@
       <c r="D1833" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="E1833" s="13">
+      <c r="E1833" s="12">
         <v>2</v>
       </c>
       <c r="F1833" s="3"/>
@@ -42557,7 +42533,7 @@
       <c r="D1834" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="E1834" s="13">
+      <c r="E1834" s="12">
         <v>3</v>
       </c>
       <c r="F1834" s="3"/>
@@ -42575,7 +42551,7 @@
       <c r="D1835" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1835" s="13" t="s">
+      <c r="E1835" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1835" s="3"/>
@@ -42737,7 +42713,7 @@
       <c r="D1844" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="E1844" s="13">
+      <c r="E1844" s="12">
         <v>1</v>
       </c>
       <c r="F1844" s="3"/>
@@ -42755,7 +42731,7 @@
       <c r="D1845" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="E1845" s="13">
+      <c r="E1845" s="12">
         <v>2</v>
       </c>
       <c r="F1845" s="3"/>
@@ -42773,7 +42749,7 @@
       <c r="D1846" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="E1846" s="13">
+      <c r="E1846" s="12">
         <v>3</v>
       </c>
       <c r="F1846" s="3"/>
@@ -42791,7 +42767,7 @@
       <c r="D1847" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1847" s="13" t="s">
+      <c r="E1847" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1847" s="3"/>
@@ -42809,8 +42785,8 @@
       <c r="D1848" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="E1848" s="13" t="s">
-        <v>2707</v>
+      <c r="E1848" s="12" t="s">
+        <v>2702</v>
       </c>
       <c r="F1848" s="3"/>
     </row>
@@ -42827,8 +42803,8 @@
       <c r="D1849" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="E1849" s="13" t="s">
-        <v>2708</v>
+      <c r="E1849" s="12" t="s">
+        <v>2703</v>
       </c>
       <c r="F1849" s="3"/>
     </row>
@@ -42845,8 +42821,8 @@
       <c r="D1850" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="E1850" s="13" t="s">
-        <v>2709</v>
+      <c r="E1850" s="12" t="s">
+        <v>2704</v>
       </c>
       <c r="F1850" s="3"/>
     </row>
@@ -42933,7 +42909,7 @@
         <v>438</v>
       </c>
       <c r="D1855" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1855" s="3">
         <v>1</v>
@@ -42953,7 +42929,7 @@
         <v>438</v>
       </c>
       <c r="D1856" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1856" s="3">
         <v>2</v>
@@ -42973,7 +42949,7 @@
         <v>438</v>
       </c>
       <c r="D1857" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1857" s="3">
         <v>3</v>
@@ -43085,7 +43061,7 @@
         <v>443</v>
       </c>
       <c r="D1863" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1863" s="3">
         <v>1</v>
@@ -43105,7 +43081,7 @@
         <v>443</v>
       </c>
       <c r="D1864" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1864" s="3">
         <v>2</v>
@@ -43125,7 +43101,7 @@
         <v>443</v>
       </c>
       <c r="D1865" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1865" s="3">
         <v>3</v>
@@ -43165,7 +43141,7 @@
         <v>438</v>
       </c>
       <c r="D1867" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1867" s="3">
         <v>1</v>
@@ -43185,7 +43161,7 @@
         <v>438</v>
       </c>
       <c r="D1868" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1868" s="3">
         <v>2</v>
@@ -43205,7 +43181,7 @@
         <v>438</v>
       </c>
       <c r="D1869" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1869" s="3">
         <v>3</v>
@@ -43225,7 +43201,7 @@
         <v>438</v>
       </c>
       <c r="D1870" s="3" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="E1870" s="3" t="s">
         <v>1337</v>
@@ -43317,7 +43293,7 @@
         <v>443</v>
       </c>
       <c r="D1875" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1875" s="3">
         <v>1</v>
@@ -43337,7 +43313,7 @@
         <v>443</v>
       </c>
       <c r="D1876" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1876" s="3">
         <v>2</v>
@@ -43357,7 +43333,7 @@
         <v>443</v>
       </c>
       <c r="D1877" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1877" s="3">
         <v>3</v>
@@ -43397,7 +43373,7 @@
         <v>438</v>
       </c>
       <c r="D1879" s="3" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="E1879" s="3">
         <v>1</v>
@@ -43417,7 +43393,7 @@
         <v>438</v>
       </c>
       <c r="D1880" s="3" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="E1880" s="3">
         <v>2</v>
@@ -43437,7 +43413,7 @@
         <v>438</v>
       </c>
       <c r="D1881" s="3" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="E1881" s="3">
         <v>3</v>
@@ -43457,7 +43433,7 @@
         <v>438</v>
       </c>
       <c r="D1882" s="3" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="E1882" s="3" t="s">
         <v>1337</v>
@@ -43531,7 +43507,7 @@
         <v>443</v>
       </c>
       <c r="D1886" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1886" s="3">
         <v>1</v>
@@ -43551,7 +43527,7 @@
         <v>443</v>
       </c>
       <c r="D1887" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1887" s="3">
         <v>2</v>
@@ -43571,7 +43547,7 @@
         <v>443</v>
       </c>
       <c r="D1888" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E1888" s="3">
         <v>3</v>
@@ -44568,7 +44544,7 @@
         <v>60</v>
       </c>
       <c r="E1943" s="3" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F1943" s="3"/>
     </row>
@@ -44598,12 +44574,12 @@
         <v>2539</v>
       </c>
       <c r="C1945" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D1945" s="3" t="s">
         <v>1349</v>
       </c>
-      <c r="E1945" s="13" t="s">
+      <c r="E1945" s="12" t="s">
         <v>2571</v>
       </c>
       <c r="F1945" s="3"/>
@@ -44616,13 +44592,13 @@
         <v>2539</v>
       </c>
       <c r="C1946" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D1946" s="3" t="s">
         <v>1366</v>
       </c>
-      <c r="E1946" s="13" t="s">
-        <v>2711</v>
+      <c r="E1946" s="12" t="s">
+        <v>2706</v>
       </c>
       <c r="F1946" s="3"/>
     </row>
@@ -44634,12 +44610,12 @@
         <v>2539</v>
       </c>
       <c r="C1947" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D1947" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1947" s="13" t="s">
+      <c r="E1947" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1947" s="3"/>
@@ -44711,7 +44687,7 @@
       <c r="D1951" s="3" t="s">
         <v>1735</v>
       </c>
-      <c r="E1951" s="13">
+      <c r="E1951" s="12">
         <v>0</v>
       </c>
       <c r="F1951" s="3"/>
@@ -44729,7 +44705,7 @@
       <c r="D1952" s="3" t="s">
         <v>1734</v>
       </c>
-      <c r="E1952" s="13">
+      <c r="E1952" s="12">
         <v>1</v>
       </c>
       <c r="F1952" s="3"/>
@@ -44747,7 +44723,7 @@
       <c r="D1953" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1953" s="13" t="s">
+      <c r="E1953" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1953" s="3"/>
@@ -45087,9 +45063,9 @@
         <v>2328</v>
       </c>
       <c r="D1972" s="3" t="s">
-        <v>2713</v>
-      </c>
-      <c r="E1972" s="13" t="s">
+        <v>2708</v>
+      </c>
+      <c r="E1972" s="12" t="s">
         <v>794</v>
       </c>
       <c r="F1972" s="3"/>
@@ -45105,9 +45081,9 @@
         <v>2328</v>
       </c>
       <c r="D1973" s="3" t="s">
-        <v>2712</v>
-      </c>
-      <c r="E1973" s="13" t="s">
+        <v>2707</v>
+      </c>
+      <c r="E1973" s="12" t="s">
         <v>795</v>
       </c>
       <c r="F1973" s="3"/>
@@ -45123,9 +45099,9 @@
         <v>2328</v>
       </c>
       <c r="D1974" s="3" t="s">
-        <v>2714</v>
-      </c>
-      <c r="E1974" s="13" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E1974" s="12" t="s">
         <v>796</v>
       </c>
       <c r="F1974" s="3"/>
@@ -45141,9 +45117,9 @@
         <v>2328</v>
       </c>
       <c r="D1975" s="3" t="s">
-        <v>2715</v>
-      </c>
-      <c r="E1975" s="13" t="s">
+        <v>2710</v>
+      </c>
+      <c r="E1975" s="12" t="s">
         <v>798</v>
       </c>
       <c r="F1975" s="3"/>
@@ -45159,9 +45135,9 @@
         <v>2328</v>
       </c>
       <c r="D1976" s="3" t="s">
-        <v>2716</v>
-      </c>
-      <c r="E1976" s="13" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E1976" s="12" t="s">
         <v>803</v>
       </c>
       <c r="F1976" s="3"/>
@@ -45179,7 +45155,7 @@
       <c r="D1977" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1977" s="13" t="s">
+      <c r="E1977" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1977" s="3"/>
@@ -45195,9 +45171,9 @@
         <v>2328</v>
       </c>
       <c r="D1978" s="3" t="s">
-        <v>2713</v>
-      </c>
-      <c r="E1978" s="13" t="s">
+        <v>2708</v>
+      </c>
+      <c r="E1978" s="12" t="s">
         <v>794</v>
       </c>
       <c r="F1978" s="3"/>
@@ -45213,9 +45189,9 @@
         <v>2328</v>
       </c>
       <c r="D1979" s="3" t="s">
-        <v>2712</v>
-      </c>
-      <c r="E1979" s="13" t="s">
+        <v>2707</v>
+      </c>
+      <c r="E1979" s="12" t="s">
         <v>795</v>
       </c>
       <c r="F1979" s="3"/>
@@ -45231,9 +45207,9 @@
         <v>2328</v>
       </c>
       <c r="D1980" s="3" t="s">
-        <v>2714</v>
-      </c>
-      <c r="E1980" s="13" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E1980" s="12" t="s">
         <v>796</v>
       </c>
       <c r="F1980" s="3"/>
@@ -45249,9 +45225,9 @@
         <v>2328</v>
       </c>
       <c r="D1981" s="3" t="s">
-        <v>2715</v>
-      </c>
-      <c r="E1981" s="13" t="s">
+        <v>2710</v>
+      </c>
+      <c r="E1981" s="12" t="s">
         <v>798</v>
       </c>
       <c r="F1981" s="3"/>
@@ -45267,9 +45243,9 @@
         <v>2328</v>
       </c>
       <c r="D1982" s="3" t="s">
-        <v>2716</v>
-      </c>
-      <c r="E1982" s="13" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E1982" s="12" t="s">
         <v>803</v>
       </c>
       <c r="F1982" s="3"/>
@@ -45285,9 +45261,9 @@
         <v>2328</v>
       </c>
       <c r="D1983" s="3" t="s">
-        <v>2718</v>
-      </c>
-      <c r="E1983" s="13" t="s">
+        <v>2713</v>
+      </c>
+      <c r="E1983" s="12" t="s">
         <v>793</v>
       </c>
       <c r="F1983" s="3"/>
@@ -45303,9 +45279,9 @@
         <v>2328</v>
       </c>
       <c r="D1984" s="3" t="s">
-        <v>2713</v>
-      </c>
-      <c r="E1984" s="13" t="s">
+        <v>2708</v>
+      </c>
+      <c r="E1984" s="12" t="s">
         <v>794</v>
       </c>
       <c r="F1984" s="3"/>
@@ -45321,9 +45297,9 @@
         <v>2328</v>
       </c>
       <c r="D1985" s="3" t="s">
-        <v>2712</v>
-      </c>
-      <c r="E1985" s="13" t="s">
+        <v>2707</v>
+      </c>
+      <c r="E1985" s="12" t="s">
         <v>795</v>
       </c>
       <c r="F1985" s="3"/>
@@ -45339,10 +45315,10 @@
         <v>2328</v>
       </c>
       <c r="D1986" s="3" t="s">
-        <v>2719</v>
-      </c>
-      <c r="E1986" s="13" t="s">
-        <v>2717</v>
+        <v>2714</v>
+      </c>
+      <c r="E1986" s="12" t="s">
+        <v>2712</v>
       </c>
       <c r="F1986" s="3"/>
     </row>
@@ -45357,9 +45333,9 @@
         <v>2328</v>
       </c>
       <c r="D1987" s="3" t="s">
-        <v>2714</v>
-      </c>
-      <c r="E1987" s="13" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E1987" s="12" t="s">
         <v>796</v>
       </c>
       <c r="F1987" s="3"/>
@@ -45375,9 +45351,9 @@
         <v>2328</v>
       </c>
       <c r="D1988" s="3" t="s">
-        <v>2715</v>
-      </c>
-      <c r="E1988" s="13" t="s">
+        <v>2710</v>
+      </c>
+      <c r="E1988" s="12" t="s">
         <v>798</v>
       </c>
       <c r="F1988" s="3"/>
@@ -45393,9 +45369,9 @@
         <v>2328</v>
       </c>
       <c r="D1989" s="3" t="s">
-        <v>2716</v>
-      </c>
-      <c r="E1989" s="13" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E1989" s="12" t="s">
         <v>803</v>
       </c>
       <c r="F1989" s="3"/>
@@ -45411,9 +45387,9 @@
         <v>2328</v>
       </c>
       <c r="D1990" s="3" t="s">
-        <v>2720</v>
-      </c>
-      <c r="E1990" s="13" t="s">
+        <v>2715</v>
+      </c>
+      <c r="E1990" s="12" t="s">
         <v>1912</v>
       </c>
       <c r="F1990" s="3"/>
@@ -45431,7 +45407,7 @@
       <c r="D1991" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E1991" s="13" t="s">
+      <c r="E1991" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F1991" s="3"/>
@@ -47120,7 +47096,7 @@
         <v>60</v>
       </c>
       <c r="E2084" s="3" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="F2084" s="3"/>
     </row>
@@ -47138,7 +47114,7 @@
         <v>60</v>
       </c>
       <c r="E2085" s="3" t="s">
-        <v>2675</v>
+        <v>2670</v>
       </c>
       <c r="F2085" s="3"/>
     </row>
@@ -47156,7 +47132,7 @@
         <v>60</v>
       </c>
       <c r="E2086" s="3" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F2086" s="3"/>
     </row>
@@ -47174,7 +47150,7 @@
         <v>60</v>
       </c>
       <c r="E2087" s="3" t="s">
-        <v>2677</v>
+        <v>2672</v>
       </c>
       <c r="F2087" s="3"/>
     </row>
@@ -47192,7 +47168,7 @@
         <v>60</v>
       </c>
       <c r="E2088" s="3" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="F2088" s="3"/>
     </row>
@@ -47210,7 +47186,7 @@
         <v>60</v>
       </c>
       <c r="E2089" s="3" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
       <c r="F2089" s="3"/>
     </row>
@@ -47228,7 +47204,7 @@
         <v>60</v>
       </c>
       <c r="E2090" s="3" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="F2090" s="3"/>
     </row>
@@ -47246,7 +47222,7 @@
         <v>60</v>
       </c>
       <c r="E2091" s="3" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="F2091" s="3"/>
     </row>
@@ -47264,7 +47240,7 @@
         <v>60</v>
       </c>
       <c r="E2092" s="3" t="s">
-        <v>2682</v>
+        <v>2677</v>
       </c>
       <c r="F2092" s="3"/>
     </row>
@@ -47282,7 +47258,7 @@
         <v>60</v>
       </c>
       <c r="E2093" s="3" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="F2093" s="3"/>
     </row>
@@ -47300,7 +47276,7 @@
         <v>60</v>
       </c>
       <c r="E2094" s="3" t="s">
-        <v>2684</v>
+        <v>2679</v>
       </c>
       <c r="F2094" s="3"/>
     </row>
@@ -47318,7 +47294,7 @@
         <v>60</v>
       </c>
       <c r="E2095" s="3" t="s">
-        <v>2685</v>
+        <v>2680</v>
       </c>
       <c r="F2095" s="3"/>
     </row>
@@ -47336,7 +47312,7 @@
         <v>60</v>
       </c>
       <c r="E2096" s="3" t="s">
-        <v>2686</v>
+        <v>2681</v>
       </c>
       <c r="F2096" s="3"/>
     </row>
@@ -47354,7 +47330,7 @@
         <v>60</v>
       </c>
       <c r="E2097" s="3" t="s">
-        <v>2687</v>
+        <v>2682</v>
       </c>
       <c r="F2097" s="3"/>
     </row>
@@ -47372,7 +47348,7 @@
         <v>60</v>
       </c>
       <c r="E2098" s="3" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="F2098" s="3"/>
     </row>
@@ -47390,7 +47366,7 @@
         <v>60</v>
       </c>
       <c r="E2099" s="3" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="F2099" s="3"/>
     </row>
@@ -47408,7 +47384,7 @@
         <v>60</v>
       </c>
       <c r="E2100" s="3" t="s">
-        <v>2690</v>
+        <v>2685</v>
       </c>
       <c r="F2100" s="3"/>
     </row>
@@ -47426,7 +47402,7 @@
         <v>60</v>
       </c>
       <c r="E2101" s="3" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="F2101" s="3"/>
     </row>
@@ -47444,7 +47420,7 @@
         <v>60</v>
       </c>
       <c r="E2102" s="3" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="F2102" s="3"/>
     </row>
@@ -47462,7 +47438,7 @@
         <v>60</v>
       </c>
       <c r="E2103" s="3" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="F2103" s="3"/>
     </row>
@@ -47480,7 +47456,7 @@
         <v>60</v>
       </c>
       <c r="E2104" s="3" t="s">
-        <v>2693</v>
+        <v>2688</v>
       </c>
       <c r="F2104" s="3"/>
     </row>
@@ -47498,7 +47474,7 @@
         <v>60</v>
       </c>
       <c r="E2105" s="3" t="s">
-        <v>2694</v>
+        <v>2689</v>
       </c>
       <c r="F2105" s="3"/>
     </row>
@@ -47516,7 +47492,7 @@
         <v>60</v>
       </c>
       <c r="E2106" s="3" t="s">
-        <v>2695</v>
+        <v>2690</v>
       </c>
       <c r="F2106" s="3"/>
     </row>
@@ -48979,7 +48955,7 @@
         <v>401</v>
       </c>
       <c r="D2187" s="3" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E2187" s="3" t="s">
         <v>1038</v>
@@ -48997,7 +48973,7 @@
         <v>401</v>
       </c>
       <c r="D2188" s="3" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E2188" s="3" t="s">
         <v>948</v>
@@ -49015,7 +48991,7 @@
         <v>401</v>
       </c>
       <c r="D2189" s="3" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E2189" s="3" t="s">
         <v>1039</v>
@@ -49033,7 +49009,7 @@
         <v>401</v>
       </c>
       <c r="D2190" s="3" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E2190" s="3" t="s">
         <v>1040</v>
@@ -49051,7 +49027,7 @@
         <v>401</v>
       </c>
       <c r="D2191" s="3" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E2191" s="3" t="s">
         <v>1337</v>
@@ -49107,7 +49083,7 @@
       <c r="D2194" s="3" t="s">
         <v>1741</v>
       </c>
-      <c r="E2194" s="13" t="s">
+      <c r="E2194" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F2194" s="3"/>
@@ -49125,7 +49101,7 @@
       <c r="D2195" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="E2195" s="13" t="s">
+      <c r="E2195" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F2195" s="3"/>
@@ -49143,7 +49119,7 @@
       <c r="D2196" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2196" s="13" t="s">
+      <c r="E2196" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2196" s="3"/>
@@ -49557,7 +49533,7 @@
       <c r="D2219" s="3" t="s">
         <v>1741</v>
       </c>
-      <c r="E2219" s="13" t="s">
+      <c r="E2219" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F2219" s="3"/>
@@ -49575,7 +49551,7 @@
       <c r="D2220" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="E2220" s="13" t="s">
+      <c r="E2220" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F2220" s="3"/>
@@ -49593,7 +49569,7 @@
       <c r="D2221" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2221" s="13" t="s">
+      <c r="E2221" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2221" s="3"/>
@@ -49611,7 +49587,7 @@
       <c r="D2222" s="3" t="s">
         <v>1741</v>
       </c>
-      <c r="E2222" s="13" t="s">
+      <c r="E2222" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F2222" s="3"/>
@@ -49629,7 +49605,7 @@
       <c r="D2223" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="E2223" s="13" t="s">
+      <c r="E2223" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F2223" s="3"/>
@@ -49647,7 +49623,7 @@
       <c r="D2224" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2224" s="13" t="s">
+      <c r="E2224" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2224" s="3"/>
@@ -49665,7 +49641,7 @@
       <c r="D2225" s="3" t="s">
         <v>1741</v>
       </c>
-      <c r="E2225" s="13" t="s">
+      <c r="E2225" s="12" t="s">
         <v>950</v>
       </c>
       <c r="F2225" s="3"/>
@@ -49683,7 +49659,7 @@
       <c r="D2226" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="E2226" s="13" t="s">
+      <c r="E2226" s="12" t="s">
         <v>956</v>
       </c>
       <c r="F2226" s="3"/>
@@ -52717,7 +52693,7 @@
         <v>2328</v>
       </c>
       <c r="D2392" s="3" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E2392" s="3" t="s">
         <v>1105</v>
@@ -52735,7 +52711,7 @@
         <v>2328</v>
       </c>
       <c r="D2393" s="3" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="E2393" s="3" t="s">
         <v>1106</v>
@@ -52789,7 +52765,7 @@
         <v>2328</v>
       </c>
       <c r="D2396" s="3" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E2396" s="3" t="s">
         <v>1105</v>
@@ -52807,7 +52783,7 @@
         <v>2328</v>
       </c>
       <c r="D2397" s="3" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="E2397" s="3" t="s">
         <v>1106</v>
@@ -52861,7 +52837,7 @@
         <v>2328</v>
       </c>
       <c r="D2400" s="3" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E2400" s="3" t="s">
         <v>1105</v>
@@ -52879,7 +52855,7 @@
         <v>2328</v>
       </c>
       <c r="D2401" s="3" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="E2401" s="3" t="s">
         <v>1106</v>
@@ -52915,7 +52891,7 @@
         <v>2328</v>
       </c>
       <c r="D2403" s="3" t="s">
-        <v>2712</v>
+        <v>2707</v>
       </c>
       <c r="E2403" s="3" t="s">
         <v>1107</v>
@@ -52933,7 +52909,7 @@
         <v>2328</v>
       </c>
       <c r="D2404" s="3" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E2404" s="3" t="s">
         <v>964</v>
@@ -52971,7 +52947,7 @@
       <c r="D2406" s="3" t="s">
         <v>2476</v>
       </c>
-      <c r="E2406" s="13">
+      <c r="E2406" s="12">
         <v>0</v>
       </c>
       <c r="F2406" s="3"/>
@@ -52989,7 +52965,7 @@
       <c r="D2407" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E2407" s="13">
+      <c r="E2407" s="12">
         <v>1</v>
       </c>
       <c r="F2407" s="3"/>
@@ -53007,7 +52983,7 @@
       <c r="D2408" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2408" s="13" t="s">
+      <c r="E2408" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2408" s="3"/>
@@ -55417,7 +55393,7 @@
         <v>2483</v>
       </c>
       <c r="D2540" s="3" t="s">
-        <v>2705</v>
+        <v>2700</v>
       </c>
       <c r="E2540" s="3" t="s">
         <v>1116</v>
@@ -55453,7 +55429,7 @@
         <v>1799</v>
       </c>
       <c r="D2542" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2542" s="3">
         <v>0</v>
@@ -55473,7 +55449,7 @@
         <v>1799</v>
       </c>
       <c r="D2543" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2543" s="3">
         <v>1</v>
@@ -55763,7 +55739,7 @@
       <c r="D2558" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="E2558" s="13" t="s">
+      <c r="E2558" s="12" t="s">
         <v>899</v>
       </c>
     </row>
@@ -55778,10 +55754,10 @@
         <v>1325</v>
       </c>
       <c r="D2559" s="3" t="s">
-        <v>2722</v>
-      </c>
-      <c r="E2559" s="13" t="s">
-        <v>2721</v>
+        <v>2717</v>
+      </c>
+      <c r="E2559" s="12" t="s">
+        <v>2716</v>
       </c>
       <c r="F2559" s="3"/>
     </row>
@@ -55798,7 +55774,7 @@
       <c r="D2560" s="3" t="s">
         <v>1370</v>
       </c>
-      <c r="E2560" s="13" t="s">
+      <c r="E2560" s="12" t="s">
         <v>899</v>
       </c>
       <c r="F2560" s="3"/>
@@ -55816,7 +55792,7 @@
       <c r="D2561" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2561" s="13" t="s">
+      <c r="E2561" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2561" s="3"/>
@@ -55886,7 +55862,7 @@
         <v>1465</v>
       </c>
       <c r="D2565" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E2565" s="3" t="s">
         <v>1473</v>
@@ -57015,7 +56991,7 @@
       <c r="C2626" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D2626" s="11" t="s">
+      <c r="D2626" s="10" t="s">
         <v>2116</v>
       </c>
       <c r="E2626" s="3">
@@ -57035,7 +57011,7 @@
       <c r="C2627" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D2627" s="11" t="s">
+      <c r="D2627" s="10" t="s">
         <v>2117</v>
       </c>
       <c r="E2627" s="3">
@@ -57055,7 +57031,7 @@
       <c r="C2628" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D2628" s="11" t="s">
+      <c r="D2628" s="10" t="s">
         <v>1336</v>
       </c>
       <c r="E2628" s="3" t="s">
@@ -57724,13 +57700,13 @@
         <v>1799</v>
       </c>
       <c r="D2665" s="3" t="s">
-        <v>2736</v>
-      </c>
-      <c r="E2665" s="13">
+        <v>2731</v>
+      </c>
+      <c r="E2665" s="12">
         <v>0</v>
       </c>
       <c r="F2665" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="2666" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -57744,13 +57720,13 @@
         <v>1799</v>
       </c>
       <c r="D2666" s="3" t="s">
-        <v>2737</v>
-      </c>
-      <c r="E2666" s="13">
+        <v>2732</v>
+      </c>
+      <c r="E2666" s="12">
         <v>1</v>
       </c>
       <c r="F2666" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="2667" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -57764,13 +57740,13 @@
         <v>1799</v>
       </c>
       <c r="D2667" s="3" t="s">
-        <v>2736</v>
-      </c>
-      <c r="E2667" s="13">
+        <v>2731</v>
+      </c>
+      <c r="E2667" s="12">
         <v>0</v>
       </c>
       <c r="F2667" s="3" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="2668" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -57784,13 +57760,13 @@
         <v>1799</v>
       </c>
       <c r="D2668" s="3" t="s">
-        <v>2737</v>
-      </c>
-      <c r="E2668" s="13">
+        <v>2732</v>
+      </c>
+      <c r="E2668" s="12">
         <v>1</v>
       </c>
       <c r="F2668" s="3" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="2669" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -57804,13 +57780,13 @@
         <v>1799</v>
       </c>
       <c r="D2669" s="3" t="s">
-        <v>2736</v>
-      </c>
-      <c r="E2669" s="13">
+        <v>2731</v>
+      </c>
+      <c r="E2669" s="12">
         <v>0</v>
       </c>
       <c r="F2669" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="2670" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -57824,13 +57800,13 @@
         <v>1799</v>
       </c>
       <c r="D2670" s="3" t="s">
-        <v>2737</v>
-      </c>
-      <c r="E2670" s="13">
+        <v>2732</v>
+      </c>
+      <c r="E2670" s="12">
         <v>1</v>
       </c>
       <c r="F2670" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="2671" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -57846,7 +57822,7 @@
       <c r="D2671" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2671" s="13" t="s">
+      <c r="E2671" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2671" s="3"/>
@@ -58388,7 +58364,7 @@
         <v>642</v>
       </c>
       <c r="D2700" s="3" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="E2700" s="3" t="s">
         <v>1142</v>
@@ -59654,7 +59630,7 @@
         <v>664</v>
       </c>
       <c r="D2769" s="3" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="E2769" s="3" t="s">
         <v>1156</v>
@@ -59671,13 +59647,13 @@
         <v>2547</v>
       </c>
       <c r="C2770" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2770" s="3" t="s">
-        <v>2730</v>
-      </c>
-      <c r="E2770" s="13" t="s">
-        <v>2724</v>
+        <v>2725</v>
+      </c>
+      <c r="E2770" s="12" t="s">
+        <v>2719</v>
       </c>
       <c r="F2770" s="3"/>
     </row>
@@ -59689,13 +59665,13 @@
         <v>2547</v>
       </c>
       <c r="C2771" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2771" s="3" t="s">
-        <v>2731</v>
-      </c>
-      <c r="E2771" s="13" t="s">
-        <v>2725</v>
+        <v>2726</v>
+      </c>
+      <c r="E2771" s="12" t="s">
+        <v>2720</v>
       </c>
       <c r="F2771" s="3"/>
     </row>
@@ -59707,13 +59683,13 @@
         <v>2547</v>
       </c>
       <c r="C2772" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2772" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E2772" s="13" t="s">
-        <v>2726</v>
+      <c r="E2772" s="12" t="s">
+        <v>2721</v>
       </c>
       <c r="F2772" s="3"/>
     </row>
@@ -59725,13 +59701,13 @@
         <v>2547</v>
       </c>
       <c r="C2773" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2773" s="3" t="s">
-        <v>2732</v>
-      </c>
-      <c r="E2773" s="13" t="s">
         <v>2727</v>
+      </c>
+      <c r="E2773" s="12" t="s">
+        <v>2722</v>
       </c>
       <c r="F2773" s="3"/>
     </row>
@@ -59743,13 +59719,13 @@
         <v>2547</v>
       </c>
       <c r="C2774" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D2774" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="E2774" s="12" t="s">
         <v>2723</v>
-      </c>
-      <c r="D2774" s="3" t="s">
-        <v>2733</v>
-      </c>
-      <c r="E2774" s="13" t="s">
-        <v>2728</v>
       </c>
       <c r="F2774" s="3"/>
     </row>
@@ -59761,13 +59737,13 @@
         <v>2547</v>
       </c>
       <c r="C2775" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2775" s="3" t="s">
         <v>1790</v>
       </c>
-      <c r="E2775" s="13" t="s">
-        <v>2729</v>
+      <c r="E2775" s="12" t="s">
+        <v>2724</v>
       </c>
       <c r="F2775" s="3"/>
     </row>
@@ -59779,12 +59755,12 @@
         <v>2547</v>
       </c>
       <c r="C2776" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2776" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2776" s="13" t="s">
+      <c r="E2776" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2776" s="3"/>
@@ -59797,13 +59773,13 @@
         <v>2547</v>
       </c>
       <c r="C2777" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2777" s="3" t="s">
-        <v>2730</v>
-      </c>
-      <c r="E2777" s="13" t="s">
-        <v>2724</v>
+        <v>2725</v>
+      </c>
+      <c r="E2777" s="12" t="s">
+        <v>2719</v>
       </c>
       <c r="F2777" s="3"/>
     </row>
@@ -59815,13 +59791,13 @@
         <v>2547</v>
       </c>
       <c r="C2778" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2778" s="3" t="s">
-        <v>2731</v>
-      </c>
-      <c r="E2778" s="13" t="s">
-        <v>2725</v>
+        <v>2726</v>
+      </c>
+      <c r="E2778" s="12" t="s">
+        <v>2720</v>
       </c>
       <c r="F2778" s="3"/>
     </row>
@@ -59833,13 +59809,13 @@
         <v>2547</v>
       </c>
       <c r="C2779" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2779" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E2779" s="13" t="s">
-        <v>2726</v>
+      <c r="E2779" s="12" t="s">
+        <v>2721</v>
       </c>
       <c r="F2779" s="3"/>
     </row>
@@ -59851,13 +59827,13 @@
         <v>2547</v>
       </c>
       <c r="C2780" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2780" s="3" t="s">
-        <v>2732</v>
-      </c>
-      <c r="E2780" s="13" t="s">
         <v>2727</v>
+      </c>
+      <c r="E2780" s="12" t="s">
+        <v>2722</v>
       </c>
       <c r="F2780" s="3"/>
     </row>
@@ -59869,13 +59845,13 @@
         <v>2547</v>
       </c>
       <c r="C2781" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D2781" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="E2781" s="12" t="s">
         <v>2723</v>
-      </c>
-      <c r="D2781" s="3" t="s">
-        <v>2733</v>
-      </c>
-      <c r="E2781" s="13" t="s">
-        <v>2728</v>
       </c>
       <c r="F2781" s="3"/>
     </row>
@@ -59887,13 +59863,13 @@
         <v>2547</v>
       </c>
       <c r="C2782" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2782" s="3" t="s">
         <v>1790</v>
       </c>
-      <c r="E2782" s="13" t="s">
-        <v>2729</v>
+      <c r="E2782" s="12" t="s">
+        <v>2724</v>
       </c>
       <c r="F2782" s="3"/>
     </row>
@@ -59905,12 +59881,12 @@
         <v>2547</v>
       </c>
       <c r="C2783" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="D2783" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="E2783" s="13" t="s">
+      <c r="E2783" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F2783" s="3"/>
@@ -61934,184 +61910,184 @@
       <c r="F2894" s="3"/>
     </row>
     <row r="2895" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2895" s="10" t="s">
+      <c r="A2895" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2895" s="11" t="s">
+      <c r="B2895" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2895" s="11" t="s">
+      <c r="C2895" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2895" s="11" t="s">
+      <c r="D2895" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2895" s="11" t="s">
+      <c r="E2895" s="10" t="s">
         <v>1233</v>
       </c>
-      <c r="F2895" s="12"/>
+      <c r="F2895" s="11"/>
     </row>
     <row r="2896" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2896" s="10" t="s">
+      <c r="A2896" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2896" s="11" t="s">
+      <c r="B2896" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2896" s="11" t="s">
+      <c r="C2896" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2896" s="11" t="s">
+      <c r="D2896" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2896" s="11" t="s">
+      <c r="E2896" s="10" t="s">
         <v>1234</v>
       </c>
-      <c r="F2896" s="12"/>
+      <c r="F2896" s="11"/>
     </row>
     <row r="2897" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2897" s="10" t="s">
+      <c r="A2897" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2897" s="11" t="s">
+      <c r="B2897" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2897" s="11" t="s">
+      <c r="C2897" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2897" s="11" t="s">
+      <c r="D2897" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2897" s="11" t="s">
+      <c r="E2897" s="10" t="s">
         <v>1235</v>
       </c>
-      <c r="F2897" s="12"/>
+      <c r="F2897" s="11"/>
     </row>
     <row r="2898" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2898" s="10" t="s">
+      <c r="A2898" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2898" s="11" t="s">
+      <c r="B2898" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2898" s="11" t="s">
+      <c r="C2898" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2898" s="11" t="s">
+      <c r="D2898" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2898" s="11" t="s">
+      <c r="E2898" s="10" t="s">
         <v>1236</v>
       </c>
-      <c r="F2898" s="12"/>
+      <c r="F2898" s="11"/>
     </row>
     <row r="2899" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2899" s="10" t="s">
+      <c r="A2899" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2899" s="11" t="s">
+      <c r="B2899" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2899" s="11" t="s">
+      <c r="C2899" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2899" s="11" t="s">
+      <c r="D2899" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2899" s="11" t="s">
+      <c r="E2899" s="10" t="s">
         <v>1237</v>
       </c>
-      <c r="F2899" s="12"/>
+      <c r="F2899" s="11"/>
     </row>
     <row r="2900" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2900" s="10" t="s">
+      <c r="A2900" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2900" s="11" t="s">
+      <c r="B2900" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2900" s="11" t="s">
+      <c r="C2900" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2900" s="11" t="s">
+      <c r="D2900" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2900" s="11" t="s">
+      <c r="E2900" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="F2900" s="12"/>
+      <c r="F2900" s="11"/>
     </row>
     <row r="2901" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2901" s="10" t="s">
+      <c r="A2901" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2901" s="11" t="s">
+      <c r="B2901" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2901" s="11" t="s">
+      <c r="C2901" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2901" s="11" t="s">
+      <c r="D2901" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2901" s="11" t="s">
+      <c r="E2901" s="10" t="s">
         <v>1239</v>
       </c>
-      <c r="F2901" s="12"/>
+      <c r="F2901" s="11"/>
     </row>
     <row r="2902" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2902" s="10" t="s">
+      <c r="A2902" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2902" s="11" t="s">
+      <c r="B2902" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2902" s="11" t="s">
+      <c r="C2902" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2902" s="11" t="s">
+      <c r="D2902" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2902" s="11" t="s">
+      <c r="E2902" s="10" t="s">
         <v>1240</v>
       </c>
-      <c r="F2902" s="12"/>
+      <c r="F2902" s="11"/>
     </row>
     <row r="2903" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2903" s="10" t="s">
+      <c r="A2903" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2903" s="11" t="s">
+      <c r="B2903" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2903" s="11" t="s">
+      <c r="C2903" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2903" s="11" t="s">
+      <c r="D2903" s="10" t="s">
         <v>2334</v>
       </c>
-      <c r="E2903" s="11" t="s">
+      <c r="E2903" s="10" t="s">
         <v>1241</v>
       </c>
-      <c r="F2903" s="12"/>
+      <c r="F2903" s="11"/>
     </row>
     <row r="2904" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2904" s="10" t="s">
+      <c r="A2904" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2904" s="11" t="s">
+      <c r="B2904" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C2904" s="11" t="s">
+      <c r="C2904" s="10" t="s">
         <v>1315</v>
       </c>
-      <c r="D2904" s="11" t="s">
+      <c r="D2904" s="10" t="s">
         <v>2398</v>
       </c>
-      <c r="E2904" s="11" t="s">
+      <c r="E2904" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="F2904" s="12"/>
+      <c r="F2904" s="11"/>
     </row>
     <row r="2905" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A2905" s="3" t="s">
@@ -63383,7 +63359,7 @@
       <c r="C2975" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2975" s="11" t="s">
+      <c r="D2975" s="10" t="s">
         <v>1469</v>
       </c>
       <c r="E2975" s="3" t="s">
@@ -63401,8 +63377,8 @@
       <c r="C2976" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2976" s="11" t="s">
-        <v>2653</v>
+      <c r="D2976" s="10" t="s">
+        <v>2650</v>
       </c>
       <c r="E2976" s="3" t="s">
         <v>1473</v>
@@ -63419,7 +63395,7 @@
       <c r="C2977" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2977" s="11" t="s">
+      <c r="D2977" s="10" t="s">
         <v>1336</v>
       </c>
       <c r="E2977" s="3" t="s">
@@ -63437,7 +63413,7 @@
       <c r="C2978" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2978" s="11" t="s">
+      <c r="D2978" s="10" t="s">
         <v>1467</v>
       </c>
       <c r="E2978" s="3" t="s">
@@ -63455,7 +63431,7 @@
       <c r="C2979" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2979" s="11" t="s">
+      <c r="D2979" s="10" t="s">
         <v>1468</v>
       </c>
       <c r="E2979" s="3" t="s">
@@ -63473,7 +63449,7 @@
       <c r="C2980" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2980" s="11" t="s">
+      <c r="D2980" s="10" t="s">
         <v>1469</v>
       </c>
       <c r="E2980" s="3" t="s">
@@ -63492,7 +63468,7 @@
         <v>1465</v>
       </c>
       <c r="D2981" s="3" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="E2981" s="3" t="s">
         <v>1473</v>
@@ -63527,7 +63503,7 @@
       <c r="C2983" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2983" s="11" t="s">
+      <c r="D2983" s="10" t="s">
         <v>1467</v>
       </c>
       <c r="E2983" s="3" t="s">
@@ -63581,8 +63557,8 @@
       <c r="C2986" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D2986" s="11" t="s">
-        <v>2653</v>
+      <c r="D2986" s="10" t="s">
+        <v>2650</v>
       </c>
       <c r="E2986" s="3" t="s">
         <v>1473</v>
@@ -63672,7 +63648,7 @@
         <v>1799</v>
       </c>
       <c r="D2991" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2991" s="3" t="s">
         <v>1969</v>
@@ -63690,7 +63666,7 @@
         <v>1799</v>
       </c>
       <c r="D2992" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2992" s="3" t="s">
         <v>1970</v>
@@ -63726,7 +63702,7 @@
         <v>1799</v>
       </c>
       <c r="D2994" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2994" s="3" t="s">
         <v>1971</v>
@@ -63744,7 +63720,7 @@
         <v>1799</v>
       </c>
       <c r="D2995" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2995" s="3" t="s">
         <v>1972</v>
@@ -63762,7 +63738,7 @@
         <v>1799</v>
       </c>
       <c r="D2996" s="3" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="E2996" s="3" t="s">
         <v>1973</v>
@@ -63816,9 +63792,9 @@
         <v>1799</v>
       </c>
       <c r="D2999" s="3" t="s">
-        <v>2661</v>
-      </c>
-      <c r="E2999" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="E2999" s="6" t="s">
         <v>949</v>
       </c>
       <c r="F2999" s="3" t="s">
@@ -63836,9 +63812,9 @@
         <v>1799</v>
       </c>
       <c r="D3000" s="3" t="s">
-        <v>2661</v>
-      </c>
-      <c r="E3000" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="E3000" s="6" t="s">
         <v>964</v>
       </c>
       <c r="F3000" s="3" t="s">
@@ -64194,10 +64170,10 @@
       <c r="B3020" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3020" s="17" t="s">
+      <c r="C3020" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="D3020" s="17" t="s">
+      <c r="D3020" s="16" t="s">
         <v>1370</v>
       </c>
       <c r="E3020" s="3" t="s">
@@ -64212,10 +64188,10 @@
       <c r="B3021" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3021" s="17" t="s">
+      <c r="C3021" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="D3021" s="18" t="s">
+      <c r="D3021" s="17" t="s">
         <v>1696</v>
       </c>
       <c r="E3021" s="3" t="s">
@@ -64230,7 +64206,7 @@
       <c r="B3022" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3022" s="17" t="s">
+      <c r="C3022" s="16" t="s">
         <v>1325</v>
       </c>
       <c r="D3022" s="3" t="s">
@@ -64248,10 +64224,10 @@
       <c r="B3023" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3023" s="17" t="s">
+      <c r="C3023" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="D3023" s="17" t="s">
+      <c r="D3023" s="16" t="s">
         <v>1370</v>
       </c>
       <c r="E3023" s="3" t="s">
@@ -64266,10 +64242,10 @@
       <c r="B3024" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3024" s="18" t="s">
+      <c r="C3024" s="17" t="s">
         <v>1325</v>
       </c>
-      <c r="D3024" s="18" t="s">
+      <c r="D3024" s="17" t="s">
         <v>1696</v>
       </c>
       <c r="E3024" s="3" t="s">
@@ -64284,7 +64260,7 @@
       <c r="B3025" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3025" s="18" t="s">
+      <c r="C3025" s="17" t="s">
         <v>1325</v>
       </c>
       <c r="D3025" s="3" t="s">
@@ -64302,10 +64278,10 @@
       <c r="B3026" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3026" s="17" t="s">
+      <c r="C3026" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="D3026" s="17" t="s">
+      <c r="D3026" s="16" t="s">
         <v>1370</v>
       </c>
       <c r="E3026" s="3" t="s">
@@ -64320,10 +64296,10 @@
       <c r="B3027" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3027" s="18" t="s">
+      <c r="C3027" s="17" t="s">
         <v>1325</v>
       </c>
-      <c r="D3027" s="18" t="s">
+      <c r="D3027" s="17" t="s">
         <v>1696</v>
       </c>
       <c r="E3027" s="3" t="s">
@@ -64338,7 +64314,7 @@
       <c r="B3028" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C3028" s="18" t="s">
+      <c r="C3028" s="17" t="s">
         <v>1325</v>
       </c>
       <c r="D3028" s="3" t="s">
@@ -64356,10 +64332,10 @@
       <c r="B3029" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C3029" s="17" t="s">
+      <c r="C3029" s="16" t="s">
         <v>1325</v>
       </c>
-      <c r="D3029" s="17" t="s">
+      <c r="D3029" s="16" t="s">
         <v>1370</v>
       </c>
       <c r="E3029" s="3" t="s">
@@ -64374,10 +64350,10 @@
       <c r="B3030" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C3030" s="18" t="s">
+      <c r="C3030" s="17" t="s">
         <v>1325</v>
       </c>
-      <c r="D3030" s="18" t="s">
+      <c r="D3030" s="17" t="s">
         <v>1696</v>
       </c>
       <c r="E3030" s="3" t="s">
@@ -64392,7 +64368,7 @@
       <c r="B3031" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C3031" s="18" t="s">
+      <c r="C3031" s="17" t="s">
         <v>1325</v>
       </c>
       <c r="D3031" s="3" t="s">
@@ -65070,191 +65046,191 @@
       <c r="F3068" s="3"/>
     </row>
     <row r="3069" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3069" s="9" t="s">
+      <c r="A3069" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B3069" s="9" t="s">
+      <c r="B3069" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3069" s="9" t="s">
+      <c r="C3069" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3069" s="9" t="s">
+      <c r="D3069" s="8" t="s">
         <v>1735</v>
       </c>
-      <c r="E3069" s="9" t="s">
+      <c r="E3069" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="F3069" s="9"/>
+      <c r="F3069" s="8"/>
     </row>
     <row r="3070" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3070" s="9" t="s">
+      <c r="A3070" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B3070" s="9" t="s">
+      <c r="B3070" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3070" s="9" t="s">
+      <c r="C3070" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3070" s="9" t="s">
+      <c r="D3070" s="8" t="s">
         <v>1734</v>
       </c>
-      <c r="E3070" s="9" t="s">
+      <c r="E3070" s="8" t="s">
         <v>1310</v>
       </c>
-      <c r="F3070" s="9"/>
+      <c r="F3070" s="8"/>
     </row>
     <row r="3071" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3071" s="9" t="s">
+      <c r="A3071" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B3071" s="9" t="s">
+      <c r="B3071" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3071" s="9" t="s">
+      <c r="C3071" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3071" s="9" t="s">
+      <c r="D3071" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="E3071" s="9" t="s">
+      <c r="E3071" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="F3071" s="9"/>
+      <c r="F3071" s="8"/>
     </row>
     <row r="3072" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3072" s="9" t="s">
+      <c r="A3072" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B3072" s="9" t="s">
+      <c r="B3072" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3072" s="9" t="s">
+      <c r="C3072" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3072" s="9" t="s">
+      <c r="D3072" s="8" t="s">
         <v>1735</v>
       </c>
-      <c r="E3072" s="9" t="s">
+      <c r="E3072" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="F3072" s="9"/>
+      <c r="F3072" s="8"/>
     </row>
     <row r="3073" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3073" s="9" t="s">
+      <c r="A3073" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B3073" s="9" t="s">
+      <c r="B3073" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3073" s="9" t="s">
+      <c r="C3073" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3073" s="9" t="s">
+      <c r="D3073" s="8" t="s">
         <v>1734</v>
       </c>
-      <c r="E3073" s="9" t="s">
+      <c r="E3073" s="8" t="s">
         <v>1310</v>
       </c>
-      <c r="F3073" s="9"/>
+      <c r="F3073" s="8"/>
     </row>
     <row r="3074" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3074" s="9" t="s">
+      <c r="A3074" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B3074" s="9" t="s">
+      <c r="B3074" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C3074" s="9" t="s">
+      <c r="C3074" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3074" s="9" t="s">
+      <c r="D3074" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="E3074" s="9" t="s">
+      <c r="E3074" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="F3074" s="9"/>
+      <c r="F3074" s="8"/>
     </row>
     <row r="3075" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3075" s="9" t="s">
+      <c r="A3075" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B3075" s="9" t="s">
+      <c r="B3075" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C3075" s="9" t="s">
+      <c r="C3075" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3075" s="9" t="s">
+      <c r="D3075" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E3075" s="9" t="s">
+      <c r="E3075" s="8" t="s">
         <v>1311</v>
       </c>
-      <c r="F3075" s="9"/>
+      <c r="F3075" s="8"/>
     </row>
     <row r="3076" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3076" s="9" t="s">
+      <c r="A3076" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B3076" s="9" t="s">
+      <c r="B3076" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C3076" s="9" t="s">
+      <c r="C3076" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3076" s="9" t="s">
+      <c r="D3076" s="8" t="s">
         <v>2371</v>
       </c>
-      <c r="E3076" s="9" t="s">
+      <c r="E3076" s="8" t="s">
         <v>1312</v>
       </c>
-      <c r="F3076" s="9"/>
+      <c r="F3076" s="8"/>
     </row>
     <row r="3077" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3077" s="9" t="s">
+      <c r="A3077" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B3077" s="9" t="s">
+      <c r="B3077" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C3077" s="9" t="s">
+      <c r="C3077" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3077" s="9" t="s">
+      <c r="D3077" s="8" t="s">
         <v>1735</v>
       </c>
-      <c r="E3077" s="9" t="s">
+      <c r="E3077" s="8" t="s">
         <v>1313</v>
       </c>
-      <c r="F3077" s="9"/>
+      <c r="F3077" s="8"/>
     </row>
     <row r="3078" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3078" s="9" t="s">
+      <c r="A3078" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B3078" s="9" t="s">
+      <c r="B3078" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C3078" s="9" t="s">
+      <c r="C3078" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D3078" s="9" t="s">
+      <c r="D3078" s="8" t="s">
         <v>1336</v>
       </c>
-      <c r="E3078" s="9" t="s">
+      <c r="E3078" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="F3078" s="9"/>
+      <c r="F3078" s="8"/>
     </row>
     <row r="3079" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3079" s="3" t="s">
         <v>202</v>
       </c>
       <c r="B3079" s="3" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="C3079" s="3" t="s">
         <v>104</v>
@@ -65263,7 +65239,7 @@
         <v>2582</v>
       </c>
       <c r="E3079" s="3" t="s">
-        <v>2743</v>
+        <v>2738</v>
       </c>
       <c r="F3079" s="3"/>
     </row>
@@ -65288,7 +65264,7 @@
         <v>227</v>
       </c>
       <c r="B3081" s="3" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="C3081" s="3" t="s">
         <v>584</v>
@@ -65297,7 +65273,7 @@
         <v>2129</v>
       </c>
       <c r="E3081" s="3" t="s">
-        <v>2744</v>
+        <v>2739</v>
       </c>
       <c r="F3081" s="3"/>
     </row>
@@ -65306,7 +65282,7 @@
         <v>227</v>
       </c>
       <c r="B3082" s="3" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="C3082" s="3" t="s">
         <v>584</v>
@@ -65315,7 +65291,7 @@
         <v>2401</v>
       </c>
       <c r="E3082" s="3" t="s">
-        <v>2745</v>
+        <v>2740</v>
       </c>
       <c r="F3082" s="3"/>
     </row>
@@ -65324,7 +65300,7 @@
         <v>1800</v>
       </c>
       <c r="B3083" s="3" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
       <c r="C3083" s="3" t="s">
         <v>1325</v>
@@ -65342,16 +65318,16 @@
         <v>1800</v>
       </c>
       <c r="B3084" s="3" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
       <c r="C3084" s="3" t="s">
         <v>1325</v>
       </c>
       <c r="D3084" s="3" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
       <c r="E3084" s="3" t="s">
-        <v>2746</v>
+        <v>2741</v>
       </c>
       <c r="F3084" s="3"/>
     </row>
@@ -65360,13 +65336,13 @@
         <v>1800</v>
       </c>
       <c r="B3085" s="3" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
       <c r="C3085" s="3" t="s">
         <v>1325</v>
       </c>
       <c r="D3085" s="3" t="s">
-        <v>2747</v>
+        <v>2742</v>
       </c>
       <c r="E3085" s="3" t="s">
         <v>1807</v>
@@ -65387,7 +65363,7 @@
         <v>1414</v>
       </c>
       <c r="E3086" s="3" t="s">
-        <v>2749</v>
+        <v>2744</v>
       </c>
       <c r="F3086" s="3"/>
     </row>
@@ -65405,7 +65381,7 @@
         <v>1412</v>
       </c>
       <c r="E3087" s="3" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
       <c r="F3087" s="3"/>
     </row>
@@ -65426,7 +65402,7 @@
         <v>899</v>
       </c>
       <c r="F3088" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="3089" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -65440,13 +65416,13 @@
         <v>146</v>
       </c>
       <c r="D3089" s="3" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
       <c r="E3089" s="3" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F3089" s="3" t="s">
         <v>2751</v>
-      </c>
-      <c r="F3089" s="3" t="s">
-        <v>2756</v>
       </c>
     </row>
     <row r="3090" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -65460,13 +65436,13 @@
         <v>146</v>
       </c>
       <c r="D3090" s="3" t="s">
-        <v>2757</v>
+        <v>2752</v>
       </c>
       <c r="E3090" s="3" t="s">
-        <v>2752</v>
+        <v>2747</v>
       </c>
       <c r="F3090" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="3091" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -65480,13 +65456,13 @@
         <v>146</v>
       </c>
       <c r="D3091" s="3" t="s">
-        <v>2760</v>
+        <v>2755</v>
       </c>
       <c r="E3091" s="3" t="s">
-        <v>2753</v>
+        <v>2748</v>
       </c>
       <c r="F3091" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="3092" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -65500,13 +65476,13 @@
         <v>146</v>
       </c>
       <c r="D3092" s="3" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
       <c r="E3092" s="3" t="s">
-        <v>2754</v>
+        <v>2749</v>
       </c>
       <c r="F3092" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="3093" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -65520,13 +65496,13 @@
         <v>146</v>
       </c>
       <c r="D3093" s="3" t="s">
-        <v>2759</v>
+        <v>2754</v>
       </c>
       <c r="E3093" s="3" t="s">
-        <v>2755</v>
+        <v>2750</v>
       </c>
       <c r="F3093" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="3094" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -65537,13 +65513,13 @@
         <v>1448</v>
       </c>
       <c r="C3094" s="3" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
       <c r="D3094" s="3" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
       <c r="E3094" s="3" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
       <c r="F3094" s="3"/>
     </row>
@@ -65555,9 +65531,9 @@
         <v>1448</v>
       </c>
       <c r="C3095" s="3" t="s">
-        <v>2765</v>
-      </c>
-      <c r="D3095" s="9" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D3095" s="8" t="s">
         <v>1336</v>
       </c>
       <c r="E3095" s="3" t="s">
@@ -65573,13 +65549,13 @@
         <v>1448</v>
       </c>
       <c r="C3096" s="3" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
       <c r="D3096" s="3" t="s">
-        <v>2763</v>
+        <v>2758</v>
       </c>
       <c r="E3096" s="3" t="s">
-        <v>2762</v>
+        <v>2757</v>
       </c>
       <c r="F3096" s="3"/>
     </row>
@@ -65591,13 +65567,13 @@
         <v>1448</v>
       </c>
       <c r="C3097" s="3" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
       <c r="D3097" s="3" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
       <c r="E3097" s="3" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
       <c r="F3097" s="3"/>
     </row>
@@ -65609,9 +65585,9 @@
         <v>1448</v>
       </c>
       <c r="C3098" s="3" t="s">
-        <v>2765</v>
-      </c>
-      <c r="D3098" s="9" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D3098" s="8" t="s">
         <v>1336</v>
       </c>
       <c r="E3098" s="3" t="s">
@@ -65627,13 +65603,13 @@
         <v>1886</v>
       </c>
       <c r="C3099" s="3" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
       <c r="D3099" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="E3099" t="s">
-        <v>2767</v>
+        <v>2762</v>
       </c>
       <c r="F3099" s="3"/>
     </row>
@@ -65645,13 +65621,13 @@
         <v>1886</v>
       </c>
       <c r="C3100" s="3" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D3100" s="3" t="s">
         <v>2766</v>
       </c>
-      <c r="D3100" s="3" t="s">
-        <v>2771</v>
-      </c>
       <c r="E3100" t="s">
-        <v>2768</v>
+        <v>2763</v>
       </c>
       <c r="F3100" s="3"/>
     </row>
@@ -65663,13 +65639,13 @@
         <v>1886</v>
       </c>
       <c r="C3101" s="3" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
       <c r="D3101" s="3" t="s">
-        <v>2772</v>
+        <v>2767</v>
       </c>
       <c r="E3101" t="s">
-        <v>2769</v>
+        <v>2764</v>
       </c>
       <c r="F3101" s="3"/>
     </row>
@@ -65681,9 +65657,9 @@
         <v>1886</v>
       </c>
       <c r="C3102" s="3" t="s">
-        <v>2766</v>
-      </c>
-      <c r="D3102" s="9" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D3102" s="8" t="s">
         <v>1336</v>
       </c>
       <c r="E3102" s="3" t="s">
@@ -65693,7 +65669,7 @@
     </row>
     <row r="3103" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3103" s="3" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="B3103" s="3" t="s">
         <v>1426</v>
@@ -65711,7 +65687,7 @@
     </row>
     <row r="3104" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3104" s="3" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="B3104" s="3" t="s">
         <v>1426</v>
@@ -65729,7 +65705,7 @@
     </row>
     <row r="3105" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3105" s="3" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="B3105" s="3" t="s">
         <v>1515</v>
@@ -65747,7 +65723,7 @@
     </row>
     <row r="3106" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3106" s="3" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="B3106" s="3" t="s">
         <v>1515</v>
@@ -65768,7 +65744,7 @@
         <v>191</v>
       </c>
       <c r="B3107" s="3" t="s">
-        <v>2742</v>
+        <v>2737</v>
       </c>
       <c r="C3107" s="3" t="s">
         <v>2444</v>
@@ -66616,7 +66592,7 @@
       <c r="D48" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="13" t="s">
         <v>2557</v>
       </c>
     </row>
@@ -67084,7 +67060,7 @@
       <c r="D75" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="13" t="s">
         <v>2549</v>
       </c>
     </row>
@@ -67215,7 +67191,7 @@
       <c r="D82" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="13" t="s">
         <v>2541</v>
       </c>
     </row>
@@ -67523,7 +67499,7 @@
         <v>948</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>2657</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -67576,7 +67552,7 @@
       <c r="D102" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E102" s="14" t="s">
+      <c r="E102" s="13" t="s">
         <v>2563</v>
       </c>
     </row>
@@ -67984,7 +67960,7 @@
         <v>2266</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -68125,7 +68101,7 @@
       <c r="D132" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E132" s="14" t="s">
+      <c r="E132" s="13" t="s">
         <v>2552</v>
       </c>
     </row>
@@ -68919,7 +68895,7 @@
       <c r="D178" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E178" s="14" t="s">
+      <c r="E178" s="13" t="s">
         <v>2554</v>
       </c>
     </row>
@@ -69177,7 +69153,7 @@
       <c r="D193" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E193" s="14" t="s">
+      <c r="E193" s="13" t="s">
         <v>2565</v>
       </c>
     </row>
@@ -69228,7 +69204,7 @@
       <c r="D196" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E196" s="14" t="s">
+      <c r="E196" s="13" t="s">
         <v>2545</v>
       </c>
     </row>
@@ -69380,7 +69356,7 @@
         <v>179</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2701</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -69522,10 +69498,10 @@
         <v>17</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>2703</v>
+        <v>2698</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="224" x14ac:dyDescent="0.2">
@@ -70020,42 +69996,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3B4BCD-1ADC-5B4E-9537-C549D7909628}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="16384" width="10.83203125" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B2" s="6" t="s">
-        <v>2654</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>2652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>2651</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>2658</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>